--- a/dataset.xlsx
+++ b/dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\office\emotion-matrix-microservices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{082141E0-E0AC-4B91-A9ED-8D64102B4E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F04D09AE-015F-4A16-8767-F24686E85DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/dataset.xlsx
+++ b/dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\office\emotion-matrix-microservices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F04D09AE-015F-4A16-8767-F24686E85DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E79ADCEF-206D-4AD4-B88B-BB5A66C1BF37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="129">
   <si>
     <t>text</t>
   </si>
@@ -49,404 +49,364 @@
     <t>models_match</t>
   </si>
   <si>
-    <t>Alex: I still cannot believe it! We actually won first place in the national hackathon competition out of over two hundred competing teams!
-Sarah: Me neither! When they called out our team name on stage, my heart skipped a beat and I wanted to scream with absolute happiness and joy!
-Alex: All those late nights coding, debugging complex race conditions, and living off black coffee finally paid off in the best possible way. Look at this magnificent trophy and the ten thousand dollar grand prize check!
-Sarah: Everyone worked so hard. Mark's machine learning model was completely flawless, and your frontend design blew the judges away during the final presentation.
-Alex: Let's call the rest of the team right now and celebrate together tonight at our favorite restaurant. We earned this massive victory!</t>
+    <t>Oh brilliant, the server crashed right as I clicked submit on my deadline.</t>
+  </si>
+  <si>
+    <t>annoyance</t>
+  </si>
+  <si>
+    <t>admiration</t>
+  </si>
+  <si>
+    <t>MATCH</t>
+  </si>
+  <si>
+    <t>Fantastic! Another mandatory two-hour meeting that could have been a three-word email.</t>
+  </si>
+  <si>
+    <t>I just love standing in the freezing rain waiting for a bus that is 45 minutes late.</t>
+  </si>
+  <si>
+    <t>disappointment</t>
+  </si>
+  <si>
+    <t>love</t>
+  </si>
+  <si>
+    <t>Wow, what a visionary design! Putting the delete button right next to the save button.</t>
+  </si>
+  <si>
+    <t>disapproval</t>
+  </si>
+  <si>
+    <t>surprise</t>
+  </si>
+  <si>
+    <t>MISMATCH</t>
+  </si>
+  <si>
+    <t>Great, my coffee spilled all over my white shirt five minutes before the interview.</t>
+  </si>
+  <si>
+    <t>Oh wonderful, the flight got delayed by another six hours in this freezing terminal.</t>
+  </si>
+  <si>
+    <t>Superb driving! You really showed that parking space who is boss by taking up three spots.</t>
+  </si>
+  <si>
+    <t>Oh fantastic, my brand new phone battery degrades after just twenty minutes of use.</t>
+  </si>
+  <si>
+    <t>I am absolutely thrilled to spend my entire Saturday fixing someone else's broken code.</t>
+  </si>
+  <si>
+    <t>excitement</t>
   </si>
   <si>
     <t>joy</t>
   </si>
   <si>
-    <t>admiration</t>
-  </si>
-  <si>
-    <t>MATCH</t>
-  </si>
-  <si>
-    <t>David: I got the heavy call from the hospital ten minutes ago. My grandmother passed away peacefully in her sleep early this morning.
-Emma: Oh David, I am so deeply sorry for your loss. I know how close you were to her and how much love she brought into your life.
-David: Thank you, Emma. It feels like a dark cloud is hanging over me. She raised me when my parents were working abroad, and walking into her quiet, empty house earlier just broke my heart into pieces.
-Emma: Take all the time you need to grieve. Don't worry about work or any deadlines right now. I'm here for you whenever you need to talk or just sit together in quiet comfort.</t>
+    <t>What a joy it is to wait on hold with customer support listening to staticky music for two hours!</t>
+  </si>
+  <si>
+    <t>anger</t>
+  </si>
+  <si>
+    <t>Oh marvelous, the Wi-Fi disconnected right during my final job interview demo.</t>
+  </si>
+  <si>
+    <t>Thank you so much for spoiling the entire movie ending right before I walked into the theater!</t>
+  </si>
+  <si>
+    <t>gratitude</t>
+  </si>
+  <si>
+    <t>Oh perfect, my umbrella turned inside out the exact second the torrential downpour started.</t>
+  </si>
+  <si>
+    <t>approval</t>
+  </si>
+  <si>
+    <t>So glad I paid premium extra for overnight shipping so it could arrive three weeks late.</t>
+  </si>
+  <si>
+    <t>Yay, another software update that completely breaks every working feature we relied on.</t>
+  </si>
+  <si>
+    <t>neutral</t>
+  </si>
+  <si>
+    <t>I am deeply touched that you remembered to invite every single person in the office except me.</t>
   </si>
   <si>
     <t>sadness</t>
   </si>
   <si>
-    <t>gratitude</t>
-  </si>
-  <si>
-    <t>MISMATCH</t>
-  </si>
-  <si>
-    <t>Mark: This is completely unacceptable! The client canceled our entire enterprise contract because your team forgot to submit the critical security audit report on time!
-Rachel: Mark, lower your voice. We experienced unexpected server downtime over the weekend that was completely out of our technical control.
-Mark: Stop making empty excuses! You had two full weeks to complete that document! You knew how critical this deadline was, yet you brushed it off like it was trivial.
-Rachel: It was not trivial! We were working around the clock under extreme pressure to resolve system outages!
-Mark: Well, now five months of hard work are down the drain, and the company lost a hundred thousand dollars because of your total negligence!</t>
-  </si>
-  <si>
-    <t>anger</t>
-  </si>
-  <si>
-    <t>annoyance</t>
-  </si>
-  <si>
-    <t>Lisa: Did you hear that loud crashing noise coming from downstairs just now? It sounded like someone shattered a glass window in the living room.
-Tom: Shh! Keep your voice down and stay behind me. The main security alarm didn't trigger, but I definitely heard heavy footstep sounds moving down the hallway.
-Lisa: Oh God, Tom, I am absolutely terrified. What if someone broke into our house with weapons? Should I dial the emergency police line right now?
-Tom: Yes, lock the bedroom door immediately and dial nine-one-one while staying low under the bed. My hands are trembling so violently right now. I'm going to grab the baseball bat, but please don't make a single sound until help arrives!</t>
+    <t>Oh super, the building air conditioner broke down on the hottest afternoon of the summer.</t>
+  </si>
+  <si>
+    <t>Oh awesome, my food order arrived two hours late, stone cold, and completely incorrect.</t>
+  </si>
+  <si>
+    <t>What a wonderful surprise, the main freeway is closed for emergency work without any detour signs.</t>
+  </si>
+  <si>
+    <t>Oh great, the elevator is broken again and my office is located on the twelfth floor.</t>
+  </si>
+  <si>
+    <t>Brilliant job leaving the fridge door wide open all night so all the groceries spoiled.</t>
+  </si>
+  <si>
+    <t>I'm having the time of my life sitting in bumper-to-bumper traffic on a hot Friday evening.</t>
+  </si>
+  <si>
+    <t>Oh how marvelous, my laptop decided to perform an automatic update during my live keynote speech.</t>
+  </si>
+  <si>
+    <t>Thanks for giving me five minutes notice before assigning a fifty-page report due tonight.</t>
+  </si>
+  <si>
+    <t>Oh superb, the hotel room smells like damp mildew and has no hot water.</t>
+  </si>
+  <si>
+    <t>disgust</t>
+  </si>
+  <si>
+    <t>I really enjoy when people talk loudly on speakerphone during a quiet train ride.</t>
+  </si>
+  <si>
+    <t>Oh wonderful, my luggage was routed to another continent while I arrived at my destination.</t>
+  </si>
+  <si>
+    <t>What a spectacular recommendation! That restaurant gave our entire group food poisoning.</t>
+  </si>
+  <si>
+    <t>Oh fantastic, the printer ran out of ink on the very last page of my legal document.</t>
+  </si>
+  <si>
+    <t>So thrilled that my noisy neighbors decided to practice heavy metal drums at 3 AM.</t>
+  </si>
+  <si>
+    <t>Oh grand, the tire blew out right when I was driving through a remote area without cellular service.</t>
   </si>
   <si>
     <t>fear</t>
   </si>
   <si>
-    <t>Jessica: Happy birthday, Michael! Turn on the lights, everyone!
-Michael: Woah! What on earth is happening here?! I thought everyone was away on a business trip for the entire weekend!
-Jessica: We pretended to be busy with work so we could set up this secret surprise party for your thirtieth birthday! And look who came—your brother flew in all the way from London just for you!
-Michael: No way! Julian, is that really you standing right here?! I am completely speechless and stunned, I had absolutely no idea whatsoever! You guys completely fooled me!
-Jessica: We've been carefully planning this secret for over three long months just to see the shocked and astonished look on your face tonight!</t>
-  </si>
-  <si>
-    <t>surprise</t>
-  </si>
-  <si>
-    <t>Elena: I wanted to drop by your office today and personally hand you this written thank-you note, Sam.
-Sam: You really didn't have to do that, Elena. What is this special note for?
-Elena: It's for staying up until three in the morning helping me rebuild my ruined presentation slides before the board meeting yesterday. Without your selfless help, I would have failed completely and lost my job.
-Sam: We are a team, Elena. I was more than happy to jump in and support you when things got tough.
-Elena: Still, your kindness, patience, and generosity mean the entire world to me. I am deeply grateful and honored to have a colleague and friend as dependable and caring as you.</t>
-  </si>
-  <si>
-    <t>Brian: Well, I just logged into the university admissions portal, and I received a rejection letter from my dream graduate program.
-Chloe: Oh no, Brian... I am so sorry. I know how tirelessly you worked for the past four years to get accepted there.
-Brian: Yeah, I maintained a top academic record, scored in the highest percentile on the entrance exams, and spent hundreds of hours volunteering. I really thought I had a strong competitive chance.
-Chloe: It feels so deeply unfair after all the personal sacrifices you made for this goal.
-Brian: It's just devastating. I feel like all my hard effort was completely in vain, and now I don't even know what direction to take next for my future.</t>
-  </si>
-  <si>
-    <t>disappointment</t>
-  </si>
-  <si>
-    <t>Karen: Can you believe our upstairs neighbor is playing blaring heavy metal music again at two in the morning on a Tuesday night?
-Jason: Ugh, this is the third time this week! I have a major corporate presentation at eight tomorrow morning and I can't sleep a single wink.
-Karen: I already walked upstairs twice earlier tonight to politely ask him to turn down the volume, but he just sneered and slammed the door right in my face.
-Jason: That is so incredibly rude, selfish, and disrespectful! Some people have zero consideration for others living in the same apartment building. I am calling the property manager and police right now to file an official noise complaint!</t>
-  </si>
-  <si>
-    <t>Dr. Aris: Look at these extraordinary electromagnetic readings coming from the deep ice core sample we extracted from Antarctica yesterday.
-Dr. Vance: Fascinating! The magnetic frequency is pulsating at precise mathematical intervals that don't match any known natural element on Earth.
-Dr. Aris: That is exactly what caught my attention. What do you think could possibly be causing such an unusual scientific phenomenon down at that extreme depth?
-Dr. Vance: I am not certain yet, but it warrants immediate rigorous investigation. Let's run a full spectrographic scan and examine the crystalline micro-structure under the high-resolution electron microscope to see what remarkable secrets this ancient ice sample holds!</t>
-  </si>
-  <si>
-    <t>curiosity</t>
-  </si>
-  <si>
-    <t>Maya: Even though our technology startup had a rough first quarter, I genuinely believe our upcoming major product release will turn everything around.
-Liam: Are you sure, Maya? Our cash reserves are running dangerously low and market competition from established tech giants is fierce right now.
-Maya: I understand your valid concerns, but our early user feedback on the beta software build has been overwhelmingly positive. The new features solve real, painful customer problems effectively.
-Liam: That is true, the initial trial signups have doubled since last week's teaser announcement.
-Maya: Exactly! If we execute our digital marketing campaign well, I am supremely confident we will bounce back stronger than ever and reach profitability very soon!</t>
-  </si>
-  <si>
-    <t>optimism</t>
-  </si>
-  <si>
-    <t>approval</t>
-  </si>
-  <si>
-    <t>Sophie: Can you please help me decipher these assembly instructions for the new bedroom wardrobe? Nothing written here makes any sense to me at all.
-Daniel: Let me see that manual... Wait, why are the step-by-step diagrams showing assembly components labelled 'Part G' when the hardware bag only contains parts up to 'Part E'?
-Sophie: That is precisely what left me so confused! And step three explicitly instructs us to attach the top panel before inserting the central support beam, which seems physically impossible.
-Daniel: This manual is completely bewildering. The text looks like it was translated poorly by a bot, and half the screw sizes listed don't match what actually came inside the box!</t>
-  </si>
-  <si>
-    <t>confusion</t>
-  </si>
-  <si>
-    <t>Hannah: Doctor, please tell us... what did the official lab biopsy results show? We've been waiting anxiously in agony for days.
-Dr. Chen: I have wonderful news for you, Hannah. The lab analysis confirmed the tissue is completely benign. There is no sign of any malignancy or disease whatsoever.
-Hannah: Oh thank God! Oh, what a tremendous weight lifted off my shoulders! I haven't been able to sleep, eat, or breathe normally thinking about the terrifying worst-case scenario.
-Dr. Chen: Everything looks clear and healthy. You can breathe easy now, you are in great shape.
-Hannah: I feel so immensely relieved and grateful. Thank you so much for putting our worried minds at ease!</t>
+    <t>I absolutely adore receiving thirty spam phone calls during my lunch break.</t>
+  </si>
+  <si>
+    <t>Oh neat, the kitchen sink burst and flooded the entire ground floor.</t>
+  </si>
+  <si>
+    <t>What a delightful experience dealing with automated phone menus that never understand a word you say!</t>
+  </si>
+  <si>
+    <t>Oh joy, my password expired and the reset link sends me into an infinite redirect loop.</t>
+  </si>
+  <si>
+    <t>How gracious of the manager to take full credit for the project I spent three months building.</t>
+  </si>
+  <si>
+    <t>Oh lovely, it started pouring rain five seconds after I finished washing and waxing my car.</t>
+  </si>
+  <si>
+    <t>So happy that the package deliverer left my fragile glass box under the leaking drainpipe.</t>
+  </si>
+  <si>
+    <t>Oh splendid, the code compiles without errors but deletes the production database instead.</t>
+  </si>
+  <si>
+    <t>I love how the landlord increased the rent by thirty percent while refusing to fix the leaky roof.</t>
+  </si>
+  <si>
+    <t>Oh outstanding, the vending machine took my last five dollars and gave me nothing in return.</t>
+  </si>
+  <si>
+    <t>What a genius idea to schedule a mandatory team building event on a Sunday morning.</t>
+  </si>
+  <si>
+    <t>Oh great, the GPS directed me straight down a narrow dead-end alley.</t>
+  </si>
+  <si>
+    <t>I just love it when people reply all to a company-wide email chain with just 'thanks'.</t>
+  </si>
+  <si>
+    <t>Oh super, my coffee cup had a micro-crack and leaked hot liquid all over my lap.</t>
+  </si>
+  <si>
+    <t>What a fantastic bargain, paying double the price for half the original portion size.</t>
+  </si>
+  <si>
+    <t>Oh marvelous, the noise cancellation on these expensive headphones amplifies high-pitched screeching instead.</t>
+  </si>
+  <si>
+    <t>So glad the store associate stared at their phone for ten minutes while I stood at the register.</t>
+  </si>
+  <si>
+    <t>Oh perfect, the gym is completely packed and every single machine is occupied by people taking selfies.</t>
+  </si>
+  <si>
+    <t>What a pleasant surprise, my alarm failed to ring because of an automatic system update reboot.</t>
+  </si>
+  <si>
+    <t>Oh terrible, you ruined my entire diet by baking the most ridiculously delicious chocolate cake!</t>
+  </si>
+  <si>
+    <t>Thanks a lot for making the rest of us look completely incompetent with your flawless presentation.</t>
+  </si>
+  <si>
+    <t>Stop being so absurdly talented, you are making all of us look like amateurs!</t>
+  </si>
+  <si>
+    <t>Oh great, now I am forced to stay up all night because this novel you recommended is too captivating.</t>
+  </si>
+  <si>
+    <t>Horrible news, I accidentally won first place in the competition and now I have to haul this giant trophy.</t>
+  </si>
+  <si>
+    <t>You really messed up big time by giving our team a surprise cash bonus right before the holidays!</t>
+  </si>
+  <si>
+    <t>I hate you so much for surprising me with front-row tickets to my absolute favorite band's concert!</t>
+  </si>
+  <si>
+    <t>Oh wonderful, now my coffee standards are ruined forever because your brew tastes too amazing.</t>
+  </si>
+  <si>
+    <t>This software is an absolute nightmare—it finished my four-hour analysis task in less than five seconds.</t>
+  </si>
+  <si>
+    <t>How dare you fix in five minutes a bug that had our senior engineering team baffled for three days!</t>
+  </si>
+  <si>
+    <t>Oh disaster! The portion size at this new restaurant is so massive I'll be eating delicious leftovers for a week.</t>
+  </si>
+  <si>
+    <t>Thanks a lot for making me cry during your speech, now everyone knows I have emotions.</t>
+  </si>
+  <si>
+    <t>Oh awful, the sun is shining so bright outside that I am forced to go enjoy a beautiful day at the beach.</t>
+  </si>
+  <si>
+    <t>You ruined my evening by making me laugh so hard that my ribs actually hurt.</t>
+  </si>
+  <si>
+    <t>amusement</t>
+  </si>
+  <si>
+    <t>Oh terrible news, we received way too many positive customer reviews and our server is overwhelmed with orders!</t>
+  </si>
+  <si>
+    <t>Stop giving such thoughtful gifts, you are setting the bar way too high for everyone else!</t>
+  </si>
+  <si>
+    <t>Oh great, now I have to find extra shelf space for all these award plaques you keep winning.</t>
+  </si>
+  <si>
+    <t>pride</t>
+  </si>
+  <si>
+    <t>This place is terrible, the dessert was so good that I had to order a second slice.</t>
+  </si>
+  <si>
+    <t>How rude of you to pay for the entire group's dinner without letting any of us chip in!</t>
+  </si>
+  <si>
+    <t>Oh catastrophic, my promotion comes with a higher salary and a corner office view.</t>
+  </si>
+  <si>
+    <t>Thanks for ruining my productivity by creating such an addictively fun video game.</t>
+  </si>
+  <si>
+    <t>Oh horrible, I asked for a small favor and you went ahead and revamped our entire codebase perfectly.</t>
+  </si>
+  <si>
+    <t>Stop making everyone else look bad with your insanely fast turnaround times!</t>
+  </si>
+  <si>
+    <t>Oh terrible, the flight landed forty minutes earlier than scheduled so now I have to wait less.</t>
   </si>
   <si>
     <t>relief</t>
   </si>
   <si>
-    <t>James: Have you seen Clara's latest humanitarian project in the news? She managed to build three solar-powered primary schools in remote villages within just six short months!
-Nora: Yes, I watched her live keynote presentation yesterday afternoon. Her relentless dedication, vision, and selfless leadership are truly inspiring to behold.
-James: She worked tirelessly without rest, raising funds day and night without ever taking a single cent of profit for herself. Her genuine passion for helping underprivileged children is unmatched anywhere.
-Nora: I have so much profound respect and admiration for her. She is a true role model who demonstrates how much positive, life-changing impact one dedicated person can bring to the world.</t>
-  </si>
-  <si>
-    <t>Ethan: I asked to meet with you today because I need to apologize from the very bottom of my heart for what I said during yesterday's department meeting.
-Grace: It really hurt and humiliated me, Ethan. You publicly criticized my project strategy in front of the entire executive leadership team.
-Ethan: I know, and it was completely wrong, insensitive, and unfair of me. I let my own personal stress and frustration get the better of me, and I foolishly projected it onto you. I feel deeply ashamed of my conduct.
-Grace: It takes courage to admit that mistake directly.
-Ethan: I sincerely regret hurting you and damaging your trust in me. I promise to do whatever it takes to make things right.</t>
-  </si>
-  <si>
-    <t>remorse</t>
-  </si>
-  <si>
-    <t>Oliver: My turn to step onto the main stage for the live television broadcast is in five minutes, and my hands are trembling uncontrollably.
-Zoe: Take a slow, deep breath, Oliver. You've prepared rigorously for weeks, and you know your presentation material inside out.
-Oliver: I know I prepared, but looking out at all those bright studio lights, camera lenses, and the live studio audience makes my stomach churn with intense knots. What if my mind goes completely blank on live air?
-Zoe: Drink a sip of water and focus on breathing steadily. You are going to do fantastically well once you start speaking. Just trust your preparation and relax!</t>
-  </si>
-  <si>
-    <t>nervousness</t>
-  </si>
-  <si>
-    <t>caring</t>
-  </si>
-  <si>
-    <t>neutral</t>
-  </si>
-  <si>
-    <t>Victor: Look at our daughter up there walking across the grand stage to receive her doctorate degree in astrophysics with highest honors!
-Sonia: I am beaming with immense pride! Do you remember when she used to stay up late as a little girl gazing at the stars through her toy telescope in our backyard?
-Victor: I remember every single detail. She worked so relentlessly for years, overcoming every academic and personal hardship to achieve her grandest dream.
-Sonia: Seeing her accomplish such an extraordinary educational milestone fills my heart with overflowing pride and joy. She has grown into a truly brilliant and remarkable woman!</t>
-  </si>
-  <si>
-    <t>pride</t>
-  </si>
-  <si>
-    <t>Robert: Good morning, I would like to inquire about the standard public operating schedule for the municipal library during the upcoming holiday weekend.
-Librarian: Certainly. The central library facility will remain open on Friday from nine in the morning until five in the evening, but we will be closed on Saturday and Sunday.
-Robert: Thank you for the information. Are the automated book return chutes operational while the main building is closed?
-Librarian: Yes, the exterior book drop box located directly next to the main entrance will remain open twenty-four hours a day for public convenience throughout the entire weekend.</t>
-  </si>
-  <si>
-    <t>Chief Architect: I have thoroughly reviewed the revised structural engineering blueprints for the eco-friendly office tower, and I must say I fully endorse this new design.
-Lead Engineer: Thank you! We completely reworked the solar ventilation system and incorporated recycled steel beams as you suggested during our last design review.
-Chief Architect: Excellent work. The updated energy efficiency ratings easily exceed our environmental sustainability goals, and the structural integrity load calculations are rock solid.
-Lead Engineer: So do we have your official authorization to move directly into the construction phase?
-Chief Architect: Absolutely. You have my full approval to proceed immediately. Outstanding work team!</t>
-  </si>
-  <si>
-    <t>Jack: You won't believe what silly thing happened when I tried to teach my golden retriever how to catch a frisbee in the park today!
-Lily: Oh no, what did he do? Did he run away across the field with it?
-Jack: Worse! He leaped high into the air, completely missed the flying frisbee, spun around twice, and landed face-first into a large pile of autumn leaves, emerging with a plastic orange pumpkin bucket stuck on his nose!
-Lily: Haha! Oh that is absolutely hysterical! I wish you had recorded that on your phone! He sounds like such a delightfully funny and adorable goofy dog!</t>
-  </si>
-  <si>
-    <t>amusement</t>
-  </si>
-  <si>
-    <t>Claire: We just opened the official confirmation letter! Our adoption application was officially approved, and we can welcome our baby boy home next week!
-Marcus: Oh Claire, this is the most wonderful news of our entire lives! I am crying tears of pure, overwhelming happiness right now!
-Claire: I know! We have waited three long, agonizing years for this dream to come true. The nursery is completely ready, and our family is finally complete!
-Marcus: Let's call our parents and friends right now to share this incredible blessing with everyone we love. I feel so immensely joyful and happy!
-Claire: This is truly the happiest day of our lives, and we will treasure this joyful moment forever!</t>
-  </si>
-  <si>
-    <t>Julian: The bakery that our family operated for over thirty wonderful years is closing its doors forever at the end of this evening.
-Maria: It truly feels like losing a beloved family member, Julian. So many cherished memories were made inside these warm walls over the decades.
-Julian: I packed up the old copper mixing bowls and turned off the main bread oven for the final time. Watching the glass display counters stand empty makes me feel hollow inside.
-Maria: We poured our heart, soul, and youth into this shop. It breaks my heart to see economic hardship force us to bid farewell to our community.</t>
-  </si>
-  <si>
-    <t>Derek: I am absolutely furious and seething with rage right now! Someone deliberately keyed the side of my brand new sports car in the office parking garage!
-Samantha: Are you serious? Did the parking lot security surveillance cameras record who committed that vandalism?
-Derek: The security guard told me that specific overhead camera has been broken for two full months! I paid thousands of dollars for that custom paint finish, and now it's completely ruined!
-Samantha: That is incredibly infuriating! Why hasn't building management fixed the security system?
-Derek: I am marching straight to the building manager's office to demand full financial compensation and accountability!</t>
-  </si>
-  <si>
-    <t>Captain: Mayday, Mayday! Flight controls are becoming unresponsive and we are experiencing severe atmospheric turbulence at thirty thousand feet altitude!
-Co-Pilot: Engine number two is overheating rapidly, Captain! Hydraulic system pressure in the primary left wing assembly is dropping towards zero!
-Captain: Initiate emergency descent protocols immediately and vector our trajectory towards the nearest military airfield! Notify air traffic control that we require priority emergency landing apparatus!
-Co-Pilot: My hands are freezing up... emergency warning lights are flashing across the cockpit display! I pray the main landing gear deploys properly under these heavy storm conditions!
-Captain: Brace for emergency landing procedures, remain securely in crash positions, and stay calm!</t>
-  </si>
-  <si>
-    <t>Rachel: Wait, look closely at this old oil painting we bought for ten dollars at the local garage sale... the art appraiser says it's an authentic original masterpiece from the nineteenth century!
-Ben: What?! Are you pulling my leg, Rachel? That dusty old canvas wrapped in the tarnished wooden frame?
-Rachel: I am completely serious! The museum art expert verified the master artist's original signature under ultraviolet light analysis. It is estimated to be worth over fifty thousand dollars!
-Ben: Holy cow! I am utterly flabbergasted and blown away! We almost threw that away into the trash bin last month!</t>
-  </si>
-  <si>
-    <t>Carlos: I wanted to take this opportunity to sincerely express how much your academic mentorship over the past year has transformed my career path, Professor Vance.
-Professor Vance: You worked exceptionally hard, Carlos. I merely helped guide your natural talent for data science and research.
-Carlos: No, your guidance went far beyond standard academic advice. You truly believed in my potential when I lacked self-confidence, and your letter helped me secure my dream fellowship.
-Professor Vance: It has been a genuine privilege watching you mature as a scholar.
-Carlos: I will forever remember your extraordinary generosity and encouragement. Thank you from the bottom of my heart.</t>
-  </si>
-  <si>
-    <t>Megan: I just finished watching the series finale episode of the epic fantasy drama we've eagerly followed for eight full seasons.
-Justin: How was it? Did the final resolution live up to all the immense fan hype and build-up?
-Megan: It was such a massive, heartbreaking letdown. The plot was terribly rushed, key character arcs were completely ruined, and major mythological mysteries were left entirely unexplained.
-Justin: That's really disheartening to hear. We spent years emotionally invested in those storyline characters.
-Megan: Exactly. I feel so deeply disappointed and frustrated that the show creators ended such a magnificent series with such lazy, uninspired writing.</t>
-  </si>
-  <si>
-    <t>Gavin: I have been stuck waiting on hold with telecommunications customer support for over an hour just to cancel a simple monthly subscription service!
-Tanya: Did any live representative answer your call yet, or are you still listening to that monotonous hold music on loop?
-Gavin: Still trapped on hold! Every five minutes an automated recording tells me 'your call is extremely important to us', yet nobody ever picks up the line!
-Tanya: That is so exasperating and manipulative. Companies deliberately make cancellation miserable so they can keep charging your credit card.
-Gavin: It's driving me crazy! I am about to hang up, call my credit card issuer directly, and block all future transactions!</t>
-  </si>
-  <si>
-    <t>Archaeologist A: Come look inside this newly unsealed stone chamber discovered behind the ancient temple wall! There are intricate hieroglyphic inscriptions we've never cataloged anywhere.
-Archaeologist B: Remarkable! The colored pigments are extraordinarily well preserved. What do these strange symbolic representations near the main altar signify?
-Archaeologist A: It appears to depict a rare astronomical alignment linked directly to a hidden underground vault beneath the stone floor slabs.
-Archaeologist B: Fascinating! Could there be untouched historical artifacts buried beneath us? Let's carefully clear the stone dust and scan the inscriptions with thermal imaging to decode their true historical meaning!
-Archaeologist A: This extraordinary discovery could rewrite everything we know about ancient history!</t>
-  </si>
-  <si>
-    <t>Simon: Our urban community garden proposal received unanimous approval from the city planning commission board tonight!
-Laura: That is fantastic news, Simon! We can finally transform that abandoned concrete lot into a vibrant green park for neighborhood families and children.
-Simon: Yes! We already have over forty local volunteers signed up to help plant organic vegetables, fruit trees, and colorful flowers starting this Saturday.
-Laura: I can already visualize neighbors coming together and children learning about nature. This wonderful project is going to bring so much health, positivity, and strong community bond to our entire area!
-Simon: Together we are turning our shared dream into a beautiful, hopeful reality for everyone!</t>
-  </si>
-  <si>
-    <t>Nathan: I am reviewing my monthly online banking statement, and there are five separate charge entries from an unknown company named 'Xylos Global Tech' that I have never heard of in my life.
-Bank Representative: Let me check our transaction database. Did you recently purchase software licenses or digital cloud storage subscriptions?
-Nathan: No, never! And the specific dollar amounts charged don't match any transaction I ever authorized. Furthermore, the transaction dates listed occurred while I was camping in the mountains completely offline!
-Bank Representative: That is certainly puzzling. Let me transfer this file immediately to our financial fraud investigation team.
-Nathan: I am completely baffled as to how my personal card details were compromised for these strange charges.</t>
-  </si>
-  <si>
-    <t>Victoria: The mountain wildfire suddenly shifted direction away from our valley just as it reached the outer residential ridge!
-Ethan: Thank heavens! So our homes, property, and neighborhood are officially safe from destruction?
-Victoria: Yes, the incident commander just announced that emergency containment lines held firm and the mandatory evacuation order has been formally lifted!
-Ethan: Oh, thank goodness... I was completely petrified that we would lose everything we owned to the raging flames. What an unimaginable sense of relief!
-Victoria: Let's head back home now, unlock the doors, and help our neighbors unpack and settle back in safely.
-Ethan: We survived the dangerous ordeal, and our community is stronger and safer than ever before!</t>
-  </si>
-  <si>
-    <t>Oliver: Did you watch the paralympic swimming championship final on television last night? The athlete who took home the gold medal competed despite losing both arms in a severe accident.
-Sophia: Yes, I watched the whole event! His incredible speed, flawless technique, and unbreakable spirit were truly awe-inspiring to witness.
-Oliver: The sheer physical determination and mental discipline required to train eight hours every day and shatter a world record under those circumstances is heroic.
-Sophia: He proved to the world that human spirit can triumph over any physical adversity. I hold boundless admiration and reverence for his unbelievable courage and achievement.</t>
-  </si>
-  <si>
-    <t>Philip: I asked to speak with you because I need to confess something difficult, Anna. I accidentally knocked over your grandmother's antique porcelain vase while moving the sofa earlier today, and it shattered into pieces.
-Anna: Oh Philip... that delicate vase was over a century old and held so much deep emotional value for my family.
-Philip: I feel absolutely terrible and sick about it. I tried to gather the pieces to repair it, but the damage is severe. I should have been infinitely more careful moving heavy furniture nearby.
-Anna: I am sad, but I appreciate that you told me the truth directly.
-Philip: I am truly, deeply sorry for my foolish carelessness.</t>
-  </si>
-  <si>
-    <t>Siddharth: My final doctoral dissertation defense before the university faculty panel begins in ten minutes, and my heart is beating violently against my chest.
-Priya: Take a calm breath, Sid. Your presentation slides are immaculate, and you have spent three rigorous years conducting this groundbreaking empirical research.
-Siddharth: I know I know the material, but Professor Henderson is infamous for asking brutal, unexpected questions designed to push candidates to their breaking point. My hands are sweating profusely.
-Priya: Drink a glass of water, keep your composure, and address each question methodically. You are thoroughly prepared, so trust in your hard work!</t>
-  </si>
-  <si>
-    <t>Engineering Director: I am thrilled to officially announce to the department that our software team successfully launched the enterprise cloud platform with zero critical bugs on day one!
-Lead Developer: We poured so many exhausting hours into refining the codebase, executing automated load testing, and optimizing database queries over the past six months.
-Engineering Director: And your dedication paid off magnificently! Executive leadership commended this deployment as the smoothest and most successful product launch in our company's history.
-Lead Developer: I feel immensely proud of what our entire team accomplished together. We set a brand new benchmark of technological excellence for the firm!</t>
-  </si>
-  <si>
-    <t>Robert: Good morning, I would like to inquire about the standard public operating schedule for the municipal library during the upcoming holiday weekend.
-Librarian: Certainly. The central library facility will remain open on Friday from nine in the morning until five in the evening, but we will be closed on Saturday and Sunday.
-Robert: Thank you for the information. Are the automated book return chutes operational while the main building is closed?
-Librarian: Yes, the exterior book drop box located directly next to the main entrance will remain open twenty-four hours a day for public convenience throughout the entire weekend.
-Robert: I appreciate your detailed assistance regarding the schedule. Have a pleasant day ahead.</t>
-  </si>
-  <si>
-    <t>Creative Director: I have thoroughly examined the updated visual brand identity materials and logo concepts your design group submitted for our corporate client.
-Lead Designer: Did the selected color palettes and modern typography choices align well with your overall vision for the brand redesign?
-Creative Director: Absolutely! The crisp typography and sleek minimal layout capture the exact sophisticated visual aesthetic we intended to achieve.
-Lead Designer: Excellent news! Should we prepare the final high-resolution vector assets for the upcoming client presentation?
-Creative Director: Yes, approved without any further revisions required. Outstanding artistic execution team, keep up this excellent standard!
-Lead Designer: Thank you so much for the approval and feedback! We will finalize the graphics package right away.</t>
-  </si>
-  <si>
-    <t>Ellie: You won't believe what hilarious thing my three-year-old toddler did during our formal dinner party with the city council last night!
-George: Oh no, what happened? Did he spill gravy all over someone's expensive outfit?
-Ellie: Worse! He placed a plastic salad bowl onto his head like a helmet, marched right up to the mayor, and loudly declared 'I am the Almighty King of Broccoli!' before making a theatrical bow!
-George: Hahaha! Oh that is completely hilarious and priceless! How did the mayor respond?
-Ellie: The entire dining room erupted into laughter! It was easily the funniest moment of the entire night!</t>
-  </si>
-  <si>
-    <t>Lucas: We just received the official patent grant document for our clean solar energy technology invention!
-Evelyn: Oh my goodness, Lucas! After five long years of grueling lab testing, patent office rejections, and endless legal revisions, it is finally officially ours!
-Lucas: Yes! The international patent office approved all twenty independent claims without a single restriction! Major clean energy investors are already calling to fund full-scale commercial manufacturing!
-Evelyn: I am literally leaping with pure joy! Our relentless hard work is going to revolutionize clean energy access across the globe! Let me pop a bottle of champagne to celebrate this glorious victory!</t>
-  </si>
-  <si>
-    <t>Beatrice: Looking through these dust-covered family photo albums from our childhood brings such a heavy, profound sense of sorrow today.
-Henry: I know how you feel, Beatrice. It's been exactly one year since Mom and Dad passed away, and the house still feels so lonely, empty, and quiet without their laughter.
-Beatrice: Every room holds precious memories of their unconditional love and warmth. I miss hearing Mom softly singing in the kitchen every morning.
-Henry: Silent tears come to my eyes whenever I walk past their favorite garden bench. Their absence leaves a deep ache in my heart that time will never erase.</t>
-  </si>
-  <si>
-    <t>Victor: This dishonest home renovation contractor took our fifty percent upfront deposit payment and completely vanished without performing any work on our kitchen!
-Clara: What?! Are you telling me he hasn't responded to any of your phone calls, text messages, or emails since last Friday?
-Victor: His business phone line has been disconnected, and when I physically drove to his registered office address, the suite was completely abandoned! He swindled us out of twenty thousand dollars!
-Clara: I am utterly enraged and boiling with fury! That money was our hard-earned family savings!
-Victor: We are filing an emergency police fraud report today and hiring an attorney to prosecute this criminal!</t>
-  </si>
-  <si>
-    <t>Hiker A: Look closely at the narrow trail bend up ahead... that is a massive wild grizzly bear with two small cubs blocking our only path down the mountain!
-Hiker B: Oh dear Lord... stay completely still where you are, do not panic, and under no circumstances run away. Mother bears are extremely aggressive when defending cubs!
-Hiker A: She just turned around and is staring directly at us! My heart is pounding like a jackhammer in my chest.
-Hiker B: Slowly step backwards inch by inch without turning your back to her. Speak in low, calm tones so she knows we aren't a threat. Pray she doesn't decide to charge at us!</t>
-  </si>
-  <si>
-    <t>Diana: Steven, quickly open this envelope! We bought a quick-pick lottery ticket yesterday on a random whim while purchasing groceries!
-Steven: Let me cross-check the winning ticket numbers on the official state lottery website... Wait... 07, 14, 22, 31, 45... Diana, re-read these numbers out loud right now!
-Diana: Are you telling me the truth?! Did we actually match all five winning numbers plus the mega bonus ball?!
-Steven: YES! We just won the ten million dollar grand jackpot prize! I cannot believe my own eyes right now! Is this an unbelievable dream or actual reality?!
-Diana: Oh my God! I am in total shock and awe! This is completely mind-blowing!</t>
-  </si>
-  <si>
-    <t>Gabriel: I wanted to take a quiet moment to express my deepest, most heartfelt appreciation to the entire medical staff who looked after me during my long stay in intensive care.
-Head Nurse: It was our absolute privilege and duty to care for you during your recovery, Gabriel. You demonstrated inspiring courage throughout.
-Gabriel: Your constant kindness, gentle words of comfort, and skilled round-the-clock medical care saved my life. I will never forget how compassionately you treated me when I was at my physically weakest point.
-Head Nurse: Seeing you walk out of this hospital in full health today is the greatest reward our nursing team could ever ask for.
-Gabriel: Thank you for everything.</t>
-  </si>
-  <si>
-    <t>Isaac: The municipal city council just voted down our community proposal for constructing a public youth sports complex in the central district.
-Vanessa: What? After all the community petitions we gathered, the town hall meetings we organized, and the detailed architectural plans we presented?
-Isaac: Yes, they voted to allocate the public municipal development budget towards building commercial parking structures instead.
-Vanessa: That is so profoundly disappointing and heart-wrenching. We spent over a full year advocating passionately for the neighborhood children who desperately need safe athletic fields.
-Isaac: It feels like a terrible step backward for our community, and I am utterly crushed by their decision.</t>
-  </si>
-  <si>
-    <t>Patrick: Our office fiber internet connection has been dropping offline every ten minutes all afternoon while I am trying to conduct crucial remote client interviews!
-Vanessa: Have you attempted rebooting the main optical router modem or contacting corporate technical support?
-Patrick: I have power-cycled that router modem five separate times already! And when I call technical support, an automated system holds me in endless diagnostic loops that fix nothing!
-Vanessa: That sounds impossibly frustrating and disruptive when you have strict client schedules to keep.
-Patrick: We pay premium enterprise rates for guaranteed high-speed fiber internet, yet the service quality is shockingly unreliable. It's driving me completely up the wall!</t>
-  </si>
-  <si>
-    <t>Astronomer A: The space telescope just transmitted high-resolution spectral data from an exoplanet located directly within the habitable zone of a nearby binary star system.
-Astronomer B: Incredible! What does the atmospheric transmission analysis indicate regarding water vapor or organic chemical biosignatures?
-Astronomer A: The initial spectroscopic absorption lines show prominent signatures of water vapor, molecular oxygen, and atmospheric ozone!
-Astronomer B: Mind-boggling! Could this distant world potentially sustain biological life forms or habitable environments? Let's process the orbital mechanics, planetary mass, and temperature profiles immediately to investigate this extraordinary discovery further!
-Astronomer A: This groundbreaking finding brings us one step closer to answering humanity's oldest question about life in the universe!</t>
-  </si>
-  <si>
-    <t>Trevor: Although our eco-friendly tech startup faced severe component supply chain delays earlier this year, our newest solar cell prototype has shattered all laboratory efficiency records.
-Julia: That is phenomenal news, Trevor! Does this breakthrough mean we can significantly lower manufacturing costs for widespread residential adoption?
-Trevor: Yes, by nearly forty-five percent! Clean solar power will now become economically accessible for millions of everyday households who previously couldn't afford renewable energy installations.
-Julia: The future of our company and planet looks so bright! We are on the precipice of driving real, massive positive change in global carbon reduction!
-Trevor: Our technological innovation will build a cleaner, greener world for future generations!</t>
-  </si>
-  <si>
-    <t>Gemma: I just unsealed my official annual tax assessment notice from the government, and the total calculated tax liability makes absolutely zero mathematical sense based on my earnings.
-Accountant: Let me carefully analyze the itemized breakdown. Wait, why did the tax authority index your home office business deductions as corporate capital gains liabilities?
-Gemma: Exactly! I filed strictly as an independent sole proprietor, yet they applied corporate tax rates while disallowing all standard business deductions.
-Accountant: This appears to be a massive processing glitch or system misclassification in their automated tax auditing algorithm.
-Gemma: I am thoroughly confused and bewildered as to how such an egregious error passed through official review.</t>
-  </si>
-  <si>
-    <t>Arthur: The mountain search and rescue team just found our lost golden retriever Rocky deep in the forest after three agonizing days of searching!
-Chloe: Oh thank God! Is he unharmed? Where did they locate him?
-Arthur: He was taking shelter near a wilderness ranger cabin five miles away, cold and hungry but completely safe, healthy, and uninjured!
-Chloe: I am crying overwhelming tears of pure relief! I couldn't sleep a single minute worrying that he was injured, frightened, or trapped in the freezing wilderness alone.
-Arthur: Let's drive out to the ranger station right now and bring our beloved dog back home. What an immense relief for our entire family!</t>
+    <t>You are absolute worst for organizing such a surprisingly incredible birthday party for me!</t>
+  </si>
+  <si>
+    <t>Oh no, my stocks went up so much today that I have to figure out tax investments.</t>
+  </si>
+  <si>
+    <t>How dare you make this complex machine learning model run on CPU with sub-millisecond latency!</t>
+  </si>
+  <si>
+    <t>Oh awful, the resort upgraded us to the presidential suite for free without even asking.</t>
+  </si>
+  <si>
+    <t>Thanks a lot, your comedy special had me gasping for air and weeping from laughter.</t>
+  </si>
+  <si>
+    <t>Oh terrible, my team completed all quarter goals two weeks ahead of schedule.</t>
+  </si>
+  <si>
+    <t>Stop being so nice to everyone, you are ruining our cynical workplace reputation!</t>
+  </si>
+  <si>
+    <t>Oh disaster, the customer service agent was so helpful that the call ended in two minutes.</t>
+  </si>
+  <si>
+    <t>You really ruined my plan of complaining today by doing everything completely right.</t>
+  </si>
+  <si>
+    <t>Oh horrible, the coffee shop gave me a free pastry just for being a loyal customer.</t>
+  </si>
+  <si>
+    <t>Thanks for destroying my self-control with these freshly baked chocolate chip cookies.</t>
+  </si>
+  <si>
+    <t>Oh terrible news, the rain stopped and a vibrant double rainbow appeared right over our house.</t>
+  </si>
+  <si>
+    <t>How obnoxious of you to write code that is so clean and self-documenting that no one needs to ask questions.</t>
+  </si>
+  <si>
+    <t>Oh no, the mechanic fixed my car's brake issue for free because it was just a loose bolt.</t>
+  </si>
+  <si>
+    <t>Stop surprising me with coffee in the morning, I might accidentally start liking mornings!</t>
+  </si>
+  <si>
+    <t>Oh awful, the movie was so engaging that two hours felt like twenty minutes.</t>
+  </si>
+  <si>
+    <t>Thanks a lot for helping me move all my heavy furniture, now I have no excuse to complain about sore muscles.</t>
+  </si>
+  <si>
+    <t>Oh terrible, this new noise-canceling headset is so quiet I can't even hear my own thoughts.</t>
+  </si>
+  <si>
+    <t>You ruined my low expectations by delivering a masterpiece of an application.</t>
+  </si>
+  <si>
+    <t>Oh no, the doctor said my health test results are so perfect I don't need to return for a year.</t>
+  </si>
+  <si>
+    <t>How dare you organize my cluttered desk so neatly while I was away at lunch!</t>
+  </si>
+  <si>
+    <t>Oh awful, the restaurant gave us complimentary champagne just because it was our anniversary.</t>
+  </si>
+  <si>
+    <t>Stop designing UI layouts that look so ridiculously good, you're making the old version look ancient.</t>
+  </si>
+  <si>
+    <t>Oh terrible, I found a hundred dollar bill in the pocket of an old jacket I haven't worn in years.</t>
+  </si>
+  <si>
+    <t>Thanks for making this complex architecture look like child's play.</t>
+  </si>
+  <si>
+    <t>Oh disaster, the exam was so easy because I studied your summary notes!</t>
   </si>
 </sst>
 </file>
@@ -799,10 +759,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="52.88671875" customWidth="1"/>
+    <col min="1" max="1" width="96.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.33203125" bestFit="1" customWidth="1"/>
@@ -853,19 +813,19 @@
         <v>11</v>
       </c>
       <c r="D2">
-        <v>0.44779999999999998</v>
+        <v>0.89439999999999997</v>
       </c>
       <c r="E2">
-        <v>129.19999999999999</v>
+        <v>47.42</v>
       </c>
       <c r="F2" t="s">
         <v>11</v>
       </c>
       <c r="G2">
-        <v>0.52659999999999996</v>
+        <v>0.39850000000000002</v>
       </c>
       <c r="H2">
-        <v>162.78</v>
+        <v>53.8</v>
       </c>
       <c r="I2" t="s">
         <v>12</v>
@@ -876,54 +836,54 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
       </c>
       <c r="D3">
-        <v>0.75749999999999995</v>
+        <v>0.94810000000000005</v>
       </c>
       <c r="E3">
-        <v>113.76</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>15</v>
+        <v>37.47</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>0.73509999999999998</v>
+        <v>0.92549999999999999</v>
       </c>
       <c r="H3">
-        <v>151.05000000000001</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>16</v>
+        <v>49.04</v>
+      </c>
+      <c r="I3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D4">
-        <v>0.40410000000000001</v>
+        <v>0.94499999999999995</v>
       </c>
       <c r="E4">
-        <v>101.94</v>
+        <v>28.15</v>
       </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G4">
-        <v>0.29330000000000001</v>
+        <v>0.96950000000000003</v>
       </c>
       <c r="H4">
-        <v>127.77</v>
+        <v>40.53</v>
       </c>
       <c r="I4" t="s">
         <v>12</v>
@@ -931,57 +891,57 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5">
+        <v>0.85450000000000004</v>
+      </c>
+      <c r="E5">
+        <v>29.82</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5">
+        <v>0.71630000000000005</v>
+      </c>
+      <c r="H5">
+        <v>43.56</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5">
-        <v>0.85740000000000005</v>
-      </c>
-      <c r="E5">
-        <v>100.7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5">
-        <v>0.62619999999999998</v>
-      </c>
-      <c r="H5">
-        <v>137.02000000000001</v>
-      </c>
-      <c r="I5" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D6">
-        <v>0.81759999999999999</v>
+        <v>0.90959999999999996</v>
       </c>
       <c r="E6">
-        <v>101.44</v>
+        <v>28.9</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>0.63160000000000005</v>
+        <v>0.91910000000000003</v>
       </c>
       <c r="H6">
-        <v>134.65</v>
+        <v>38.14</v>
       </c>
       <c r="I6" t="s">
         <v>12</v>
@@ -989,86 +949,86 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>11</v>
       </c>
       <c r="D7">
-        <v>0.26600000000000001</v>
+        <v>0.55269999999999997</v>
       </c>
       <c r="E7">
-        <v>103.86</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>15</v>
+        <v>30.22</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>0.84709999999999996</v>
+        <v>0.79920000000000002</v>
       </c>
       <c r="H7">
-        <v>137.08000000000001</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>16</v>
+        <v>36.479999999999997</v>
+      </c>
+      <c r="I7" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
       </c>
       <c r="D8">
-        <v>0.63190000000000002</v>
+        <v>0.92889999999999995</v>
       </c>
       <c r="E8">
-        <v>100.81</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>26</v>
+        <v>38.86</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
       </c>
       <c r="G8">
-        <v>0.45519999999999999</v>
+        <v>0.94310000000000005</v>
       </c>
       <c r="H8">
-        <v>130.56</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>16</v>
+        <v>56.52</v>
+      </c>
+      <c r="I8" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D9">
-        <v>0.64170000000000005</v>
+        <v>0.81310000000000004</v>
       </c>
       <c r="E9">
-        <v>97.17</v>
+        <v>33.130000000000003</v>
       </c>
       <c r="F9" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G9">
-        <v>0.40439999999999998</v>
+        <v>0.77510000000000001</v>
       </c>
       <c r="H9">
-        <v>129.65</v>
+        <v>47.54</v>
       </c>
       <c r="I9" t="s">
         <v>12</v>
@@ -1076,57 +1036,57 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" t="s">
-        <v>29</v>
+        <v>10</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="D10">
-        <v>0.5887</v>
+        <v>0.64119999999999999</v>
       </c>
       <c r="E10">
-        <v>102.14</v>
-      </c>
-      <c r="F10" t="s">
-        <v>29</v>
+        <v>31.6</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="G10">
-        <v>0.61439999999999995</v>
+        <v>0.81489999999999996</v>
       </c>
       <c r="H10">
-        <v>123.13</v>
-      </c>
-      <c r="I10" t="s">
-        <v>12</v>
+        <v>42.59</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D11">
-        <v>0.74860000000000004</v>
+        <v>0.85029999999999994</v>
       </c>
       <c r="E11">
-        <v>97.92</v>
+        <v>34.78</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G11">
-        <v>0.62629999999999997</v>
+        <v>0.88380000000000003</v>
       </c>
       <c r="H11">
-        <v>129.33000000000001</v>
+        <v>43.08</v>
       </c>
       <c r="I11" t="s">
         <v>12</v>
@@ -1134,57 +1094,57 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" t="s">
-        <v>34</v>
+        <v>15</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="D12">
-        <v>0.92300000000000004</v>
+        <v>0.81110000000000004</v>
       </c>
       <c r="E12">
-        <v>99.24</v>
-      </c>
-      <c r="F12" t="s">
-        <v>34</v>
+        <v>30.71</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G12">
-        <v>0.82189999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H12">
-        <v>128.69</v>
-      </c>
-      <c r="I12" t="s">
-        <v>12</v>
+        <v>42.36</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D13">
-        <v>0.49690000000000001</v>
+        <v>0.98740000000000006</v>
       </c>
       <c r="E13">
-        <v>95.48</v>
+        <v>33.29</v>
       </c>
       <c r="F13" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="G13">
-        <v>0.85109999999999997</v>
+        <v>0.99980000000000002</v>
       </c>
       <c r="H13">
-        <v>128.59</v>
+        <v>47.39</v>
       </c>
       <c r="I13" t="s">
         <v>12</v>
@@ -1192,57 +1152,57 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="D14">
-        <v>0.9163</v>
+        <v>0.45019999999999999</v>
       </c>
       <c r="E14">
-        <v>92.94</v>
-      </c>
-      <c r="F14" t="s">
+        <v>38.68</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G14">
-        <v>0.90280000000000005</v>
+        <v>0.62670000000000003</v>
       </c>
       <c r="H14">
-        <v>128.80000000000001</v>
-      </c>
-      <c r="I14" t="s">
-        <v>12</v>
+        <v>42.36</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="D15">
-        <v>0.42970000000000003</v>
+        <v>0.7177</v>
       </c>
       <c r="E15">
-        <v>95.12</v>
+        <v>31.55</v>
       </c>
       <c r="F15" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="G15">
-        <v>0.41339999999999999</v>
+        <v>0.76690000000000003</v>
       </c>
       <c r="H15">
-        <v>130</v>
+        <v>37.33</v>
       </c>
       <c r="I15" t="s">
         <v>12</v>
@@ -1250,57 +1210,57 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="D16">
-        <v>0.25459999999999999</v>
+        <v>0.38700000000000001</v>
       </c>
       <c r="E16">
-        <v>96</v>
+        <v>27.51</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G16">
-        <v>0.30470000000000003</v>
+        <v>0.21160000000000001</v>
       </c>
       <c r="H16">
-        <v>121.91</v>
+        <v>37.74</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C17" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="D17">
-        <v>0.70030000000000003</v>
+        <v>0.38979999999999998</v>
       </c>
       <c r="E17">
-        <v>228.48</v>
+        <v>31.16</v>
       </c>
       <c r="F17" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="G17">
-        <v>0.83069999999999999</v>
+        <v>0.26529999999999998</v>
       </c>
       <c r="H17">
-        <v>120.1</v>
+        <v>39.96</v>
       </c>
       <c r="I17" t="s">
         <v>12</v>
@@ -1308,28 +1268,28 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B18" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D18">
-        <v>0.74860000000000004</v>
+        <v>0.55220000000000002</v>
       </c>
       <c r="E18">
-        <v>87.69</v>
+        <v>29.85</v>
       </c>
       <c r="F18" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G18">
-        <v>0.92630000000000001</v>
+        <v>0.2064</v>
       </c>
       <c r="H18">
-        <v>113.37</v>
+        <v>40.21</v>
       </c>
       <c r="I18" t="s">
         <v>12</v>
@@ -1337,28 +1297,28 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="C19" t="s">
         <v>11</v>
       </c>
       <c r="D19">
-        <v>0.69969999999999999</v>
+        <v>0.4667</v>
       </c>
       <c r="E19">
-        <v>93.14</v>
+        <v>29.71</v>
       </c>
       <c r="F19" t="s">
         <v>11</v>
       </c>
       <c r="G19">
-        <v>0.81410000000000005</v>
+        <v>0.65839999999999999</v>
       </c>
       <c r="H19">
-        <v>122.38</v>
+        <v>38.24</v>
       </c>
       <c r="I19" t="s">
         <v>12</v>
@@ -1366,28 +1326,28 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B20" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="D20">
-        <v>0.77810000000000001</v>
+        <v>0.85729999999999995</v>
       </c>
       <c r="E20">
-        <v>96.39</v>
+        <v>28.48</v>
       </c>
       <c r="F20" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="G20">
-        <v>0.60229999999999995</v>
+        <v>0.95920000000000005</v>
       </c>
       <c r="H20">
-        <v>122.84</v>
+        <v>36.75</v>
       </c>
       <c r="I20" t="s">
         <v>12</v>
@@ -1395,28 +1355,28 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B21" t="s">
         <v>10</v>
       </c>
       <c r="C21" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D21">
         <v>0.78339999999999999</v>
       </c>
       <c r="E21">
-        <v>99.32</v>
+        <v>28.45</v>
       </c>
       <c r="F21" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G21">
-        <v>0.79379999999999995</v>
+        <v>0.79010000000000002</v>
       </c>
       <c r="H21">
-        <v>124.89</v>
+        <v>41.05</v>
       </c>
       <c r="I21" t="s">
         <v>12</v>
@@ -1424,28 +1384,28 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B22" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D22">
-        <v>0.89249999999999996</v>
+        <v>0.94369999999999998</v>
       </c>
       <c r="E22">
-        <v>88.28</v>
+        <v>26.09</v>
       </c>
       <c r="F22" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G22">
-        <v>0.56920000000000004</v>
+        <v>0.95540000000000003</v>
       </c>
       <c r="H22">
-        <v>117.88</v>
+        <v>41.49</v>
       </c>
       <c r="I22" t="s">
         <v>12</v>
@@ -1453,28 +1413,28 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B23" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C23" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D23">
-        <v>0.73309999999999997</v>
+        <v>0.73839999999999995</v>
       </c>
       <c r="E23">
-        <v>95.89</v>
+        <v>27.91</v>
       </c>
       <c r="F23" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G23">
-        <v>0.65590000000000004</v>
+        <v>0.66790000000000005</v>
       </c>
       <c r="H23">
-        <v>126.16</v>
+        <v>41.25</v>
       </c>
       <c r="I23" t="s">
         <v>12</v>
@@ -1482,86 +1442,86 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B24" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>42</v>
+        <v>10</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
       </c>
       <c r="D24">
-        <v>0.58730000000000004</v>
+        <v>0.74809999999999999</v>
       </c>
       <c r="E24">
-        <v>94.5</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>43</v>
+        <v>28.43</v>
+      </c>
+      <c r="F24" t="s">
+        <v>11</v>
       </c>
       <c r="G24">
-        <v>0.25580000000000003</v>
+        <v>0.75819999999999999</v>
       </c>
       <c r="H24">
-        <v>129.91</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>16</v>
+        <v>36.450000000000003</v>
+      </c>
+      <c r="I24" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B25" t="s">
-        <v>23</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
+      </c>
+      <c r="C25" t="s">
+        <v>32</v>
       </c>
       <c r="D25">
-        <v>0.54920000000000002</v>
+        <v>0.98609999999999998</v>
       </c>
       <c r="E25">
-        <v>88.62</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>29</v>
+        <v>27.39</v>
+      </c>
+      <c r="F25" t="s">
+        <v>32</v>
       </c>
       <c r="G25">
-        <v>0.41360000000000002</v>
+        <v>0.99950000000000006</v>
       </c>
       <c r="H25">
-        <v>119.62</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>16</v>
+        <v>40.64</v>
+      </c>
+      <c r="I25" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B26" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="C26" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D26">
-        <v>0.71789999999999998</v>
+        <v>0.71640000000000004</v>
       </c>
       <c r="E26">
-        <v>92.61</v>
+        <v>29.21</v>
       </c>
       <c r="F26" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G26">
-        <v>0.94730000000000003</v>
+        <v>0.85170000000000001</v>
       </c>
       <c r="H26">
-        <v>125.61</v>
+        <v>44.64</v>
       </c>
       <c r="I26" t="s">
         <v>12</v>
@@ -1569,57 +1529,57 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
+      </c>
+      <c r="C27" t="s">
+        <v>27</v>
       </c>
       <c r="D27">
-        <v>0.73380000000000001</v>
+        <v>0.89980000000000004</v>
       </c>
       <c r="E27">
-        <v>95.08</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>26</v>
+        <v>29.29</v>
+      </c>
+      <c r="F27" t="s">
+        <v>27</v>
       </c>
       <c r="G27">
-        <v>0.84399999999999997</v>
+        <v>0.98099999999999998</v>
       </c>
       <c r="H27">
-        <v>126.07</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>16</v>
+        <v>39.799999999999997</v>
+      </c>
+      <c r="I27" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B28" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C28" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D28">
-        <v>0.5998</v>
+        <v>0.72850000000000004</v>
       </c>
       <c r="E28">
-        <v>96.44</v>
+        <v>28.38</v>
       </c>
       <c r="F28" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G28">
-        <v>0.50829999999999997</v>
+        <v>0.66069999999999995</v>
       </c>
       <c r="H28">
-        <v>121.56</v>
+        <v>40.68</v>
       </c>
       <c r="I28" t="s">
         <v>12</v>
@@ -1627,57 +1587,57 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>29</v>
+        <v>49</v>
+      </c>
+      <c r="C29" t="s">
+        <v>11</v>
       </c>
       <c r="D29">
-        <v>0.5151</v>
+        <v>0.76</v>
       </c>
       <c r="E29">
-        <v>101.21</v>
-      </c>
-      <c r="F29" s="1" t="s">
+        <v>27.12</v>
+      </c>
+      <c r="F29" t="s">
         <v>11</v>
       </c>
       <c r="G29">
-        <v>0.72629999999999995</v>
+        <v>0.8982</v>
       </c>
       <c r="H29">
-        <v>131.30000000000001</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>16</v>
+        <v>34.35</v>
+      </c>
+      <c r="I29" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B30" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="C30" t="s">
         <v>11</v>
       </c>
       <c r="D30">
-        <v>0.6613</v>
+        <v>0.85829999999999995</v>
       </c>
       <c r="E30">
-        <v>99.23</v>
+        <v>28.38</v>
       </c>
       <c r="F30" t="s">
         <v>11</v>
       </c>
       <c r="G30">
-        <v>0.63009999999999999</v>
+        <v>0.81710000000000005</v>
       </c>
       <c r="H30">
-        <v>121.42</v>
+        <v>37.97</v>
       </c>
       <c r="I30" t="s">
         <v>12</v>
@@ -1685,28 +1645,28 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C31" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D31">
-        <v>0.51829999999999998</v>
+        <v>0.58699999999999997</v>
       </c>
       <c r="E31">
-        <v>95.95</v>
+        <v>27.47</v>
       </c>
       <c r="F31" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G31">
-        <v>0.43490000000000001</v>
+        <v>0.69159999999999999</v>
       </c>
       <c r="H31">
-        <v>122.57</v>
+        <v>34.76</v>
       </c>
       <c r="I31" t="s">
         <v>12</v>
@@ -1714,57 +1674,57 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B32" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="D32">
-        <v>0.32740000000000002</v>
+        <v>0.27200000000000002</v>
       </c>
       <c r="E32">
-        <v>93.96</v>
+        <v>28.36</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G32">
-        <v>0.56079999999999997</v>
+        <v>0.20019999999999999</v>
       </c>
       <c r="H32">
-        <v>128.77000000000001</v>
+        <v>40.61</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B33" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C33" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D33">
-        <v>0.91679999999999995</v>
+        <v>0.94450000000000001</v>
       </c>
       <c r="E33">
-        <v>97.03</v>
+        <v>25</v>
       </c>
       <c r="F33" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G33">
-        <v>0.93230000000000002</v>
+        <v>0.5353</v>
       </c>
       <c r="H33">
-        <v>122.91</v>
+        <v>38.409999999999997</v>
       </c>
       <c r="I33" t="s">
         <v>12</v>
@@ -1772,28 +1732,28 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B34" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="C34" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="D34">
-        <v>0.78459999999999996</v>
+        <v>0.12239999999999999</v>
       </c>
       <c r="E34">
-        <v>95.84</v>
+        <v>26.77</v>
       </c>
       <c r="F34" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="G34">
-        <v>0.75700000000000001</v>
+        <v>0.32169999999999999</v>
       </c>
       <c r="H34">
-        <v>122.03</v>
+        <v>37.369999999999997</v>
       </c>
       <c r="I34" t="s">
         <v>12</v>
@@ -1801,57 +1761,57 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B35" t="s">
-        <v>41</v>
-      </c>
-      <c r="C35" t="s">
-        <v>43</v>
+        <v>10</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="D35">
-        <v>0.47299999999999998</v>
+        <v>0.75249999999999995</v>
       </c>
       <c r="E35">
-        <v>94.76</v>
-      </c>
-      <c r="F35" t="s">
-        <v>43</v>
+        <v>26.5</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="G35">
-        <v>0.31180000000000002</v>
+        <v>0.69399999999999995</v>
       </c>
       <c r="H35">
-        <v>123.4</v>
-      </c>
-      <c r="I35" t="s">
-        <v>12</v>
+        <v>43.23</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="C36" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D36">
-        <v>0.66679999999999995</v>
+        <v>0.78480000000000005</v>
       </c>
       <c r="E36">
-        <v>92.53</v>
+        <v>31.74</v>
       </c>
       <c r="F36" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="G36">
-        <v>0.69159999999999999</v>
+        <v>0.52390000000000003</v>
       </c>
       <c r="H36">
-        <v>119.31</v>
+        <v>50.53</v>
       </c>
       <c r="I36" t="s">
         <v>12</v>
@@ -1859,28 +1819,28 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B37" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="C37" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D37">
-        <v>0.77470000000000006</v>
+        <v>0.84989999999999999</v>
       </c>
       <c r="E37">
-        <v>90.21</v>
+        <v>41.73</v>
       </c>
       <c r="F37" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G37">
-        <v>0.95509999999999995</v>
+        <v>0.7218</v>
       </c>
       <c r="H37">
-        <v>118.17</v>
+        <v>48.76</v>
       </c>
       <c r="I37" t="s">
         <v>12</v>
@@ -1888,57 +1848,57 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B38" t="s">
-        <v>32</v>
-      </c>
-      <c r="C38" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="C38" t="s">
+        <v>16</v>
+      </c>
       <c r="D38">
-        <v>0.58450000000000002</v>
+        <v>0.67159999999999997</v>
       </c>
       <c r="E38">
-        <v>99.59</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>11</v>
+        <v>34.229999999999997</v>
+      </c>
+      <c r="F38" t="s">
+        <v>16</v>
       </c>
       <c r="G38">
-        <v>0.72709999999999997</v>
+        <v>0.37019999999999997</v>
       </c>
       <c r="H38">
-        <v>142.71</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>16</v>
+        <v>48.84</v>
+      </c>
+      <c r="I38" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="C39" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="D39">
-        <v>0.9194</v>
+        <v>0.72030000000000005</v>
       </c>
       <c r="E39">
-        <v>102.49</v>
+        <v>28.78</v>
       </c>
       <c r="F39" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="G39">
-        <v>0.8125</v>
+        <v>0.94730000000000003</v>
       </c>
       <c r="H39">
-        <v>123.95</v>
+        <v>39.89</v>
       </c>
       <c r="I39" t="s">
         <v>12</v>
@@ -1946,28 +1906,28 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B40" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C40" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D40">
-        <v>0.54510000000000003</v>
+        <v>0.86960000000000004</v>
       </c>
       <c r="E40">
-        <v>94.07</v>
+        <v>26.82</v>
       </c>
       <c r="F40" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G40">
-        <v>0.47949999999999998</v>
+        <v>0.86560000000000004</v>
       </c>
       <c r="H40">
-        <v>125.98</v>
+        <v>41.93</v>
       </c>
       <c r="I40" t="s">
         <v>12</v>
@@ -1975,28 +1935,28 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B41" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="C41" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D41">
-        <v>0.89649999999999996</v>
+        <v>0.89400000000000002</v>
       </c>
       <c r="E41">
-        <v>89.24</v>
+        <v>29.26</v>
       </c>
       <c r="F41" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G41">
-        <v>0.85019999999999996</v>
+        <v>0.95040000000000002</v>
       </c>
       <c r="H41">
-        <v>112.03</v>
+        <v>39.79</v>
       </c>
       <c r="I41" t="s">
         <v>12</v>
@@ -2004,57 +1964,57 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B42" t="s">
-        <v>18</v>
-      </c>
-      <c r="C42" t="s">
-        <v>18</v>
+        <v>10</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="D42">
-        <v>0.50460000000000005</v>
+        <v>0.28620000000000001</v>
       </c>
       <c r="E42">
-        <v>91.12</v>
-      </c>
-      <c r="F42" t="s">
-        <v>18</v>
+        <v>26.51</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="G42">
-        <v>0.31990000000000002</v>
+        <v>0.35460000000000003</v>
       </c>
       <c r="H42">
-        <v>119.87</v>
-      </c>
-      <c r="I42" t="s">
-        <v>12</v>
+        <v>38.049999999999997</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B43" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C43" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="D43">
-        <v>0.58099999999999996</v>
+        <v>0.91779999999999995</v>
       </c>
       <c r="E43">
-        <v>92.23</v>
+        <v>25.33</v>
       </c>
       <c r="F43" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="G43">
-        <v>0.47489999999999999</v>
+        <v>0.91139999999999999</v>
       </c>
       <c r="H43">
-        <v>125.41</v>
+        <v>34.97</v>
       </c>
       <c r="I43" t="s">
         <v>12</v>
@@ -2062,115 +2022,115 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B44" t="s">
-        <v>23</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
+      </c>
+      <c r="C44" t="s">
+        <v>11</v>
       </c>
       <c r="D44">
-        <v>0.46579999999999999</v>
+        <v>0.9163</v>
       </c>
       <c r="E44">
-        <v>101.24</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>29</v>
+        <v>28.35</v>
+      </c>
+      <c r="F44" t="s">
+        <v>11</v>
       </c>
       <c r="G44">
-        <v>0.37330000000000002</v>
+        <v>0.93210000000000004</v>
       </c>
       <c r="H44">
-        <v>132.02000000000001</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>16</v>
+        <v>37.29</v>
+      </c>
+      <c r="I44" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B45" t="s">
-        <v>15</v>
-      </c>
-      <c r="C45" t="s">
-        <v>15</v>
+        <v>10</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="D45">
-        <v>0.82479999999999998</v>
+        <v>0.92100000000000004</v>
       </c>
       <c r="E45">
-        <v>94.21</v>
-      </c>
-      <c r="F45" t="s">
-        <v>15</v>
+        <v>28.26</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="G45">
-        <v>0.8498</v>
+        <v>0.92949999999999999</v>
       </c>
       <c r="H45">
-        <v>121.06</v>
-      </c>
-      <c r="I45" t="s">
-        <v>12</v>
+        <v>43.43</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B46" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C46" t="s">
-        <v>26</v>
-      </c>
       <c r="D46">
-        <v>0.60529999999999995</v>
+        <v>0.21640000000000001</v>
       </c>
       <c r="E46">
-        <v>94.12</v>
-      </c>
-      <c r="F46" t="s">
-        <v>26</v>
+        <v>31.95</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G46">
-        <v>0.73960000000000004</v>
+        <v>0.19</v>
       </c>
       <c r="H46">
-        <v>129.36000000000001</v>
-      </c>
-      <c r="I46" t="s">
-        <v>12</v>
+        <v>41.96</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B47" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C47" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D47">
-        <v>0.61450000000000005</v>
+        <v>0.93010000000000004</v>
       </c>
       <c r="E47">
-        <v>95.97</v>
+        <v>28.53</v>
       </c>
       <c r="F47" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G47">
-        <v>0.49220000000000003</v>
+        <v>0.96709999999999996</v>
       </c>
       <c r="H47">
-        <v>126.38</v>
+        <v>32.340000000000003</v>
       </c>
       <c r="I47" t="s">
         <v>12</v>
@@ -2178,28 +2138,28 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B48" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C48" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="D48">
-        <v>0.49459999999999998</v>
+        <v>0.9002</v>
       </c>
       <c r="E48">
-        <v>101.93</v>
+        <v>30.42</v>
       </c>
       <c r="F48" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="G48">
-        <v>0.65790000000000004</v>
+        <v>0.84689999999999999</v>
       </c>
       <c r="H48">
-        <v>137</v>
+        <v>46.41</v>
       </c>
       <c r="I48" t="s">
         <v>12</v>
@@ -2207,28 +2167,28 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B49" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="C49" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D49">
-        <v>0.3649</v>
+        <v>0.6643</v>
       </c>
       <c r="E49">
-        <v>119.75</v>
+        <v>27.9</v>
       </c>
       <c r="F49" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="G49">
-        <v>0.61250000000000004</v>
+        <v>0.8417</v>
       </c>
       <c r="H49">
-        <v>124.82</v>
+        <v>40.81</v>
       </c>
       <c r="I49" t="s">
         <v>12</v>
@@ -2236,28 +2196,28 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B50" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="C50" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D50">
-        <v>0.89239999999999997</v>
+        <v>0.78520000000000001</v>
       </c>
       <c r="E50">
-        <v>97.32</v>
+        <v>30.54</v>
       </c>
       <c r="F50" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="G50">
-        <v>0.72699999999999998</v>
+        <v>0.67649999999999999</v>
       </c>
       <c r="H50">
-        <v>125.14</v>
+        <v>40.96</v>
       </c>
       <c r="I50" t="s">
         <v>12</v>
@@ -2265,31 +2225,1481 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>75</v>
+      </c>
+      <c r="B51" t="s">
+        <v>15</v>
+      </c>
+      <c r="C51" t="s">
+        <v>19</v>
+      </c>
+      <c r="D51">
+        <v>0.84019999999999995</v>
+      </c>
+      <c r="E51">
+        <v>26.87</v>
+      </c>
+      <c r="F51" t="s">
+        <v>19</v>
+      </c>
+      <c r="G51">
+        <v>0.94540000000000002</v>
+      </c>
+      <c r="H51">
+        <v>35.590000000000003</v>
+      </c>
+      <c r="I51" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>76</v>
+      </c>
+      <c r="B52" t="s">
+        <v>27</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D52">
+        <v>0.20169999999999999</v>
+      </c>
+      <c r="E52">
+        <v>28.13</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G52">
+        <v>0.45129999999999998</v>
+      </c>
+      <c r="H52">
+        <v>37.01</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>77</v>
+      </c>
+      <c r="B53" t="s">
+        <v>11</v>
+      </c>
+      <c r="C53" t="s">
+        <v>32</v>
+      </c>
+      <c r="D53">
+        <v>0.98729999999999996</v>
+      </c>
+      <c r="E53">
+        <v>28</v>
+      </c>
+      <c r="F53" t="s">
+        <v>32</v>
+      </c>
+      <c r="G53">
+        <v>0.99790000000000001</v>
+      </c>
+      <c r="H53">
+        <v>37.07</v>
+      </c>
+      <c r="I53" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>78</v>
+      </c>
+      <c r="B54" t="s">
+        <v>11</v>
+      </c>
+      <c r="C54" t="s">
+        <v>10</v>
+      </c>
+      <c r="D54">
+        <v>0.57279999999999998</v>
+      </c>
+      <c r="E54">
+        <v>27.48</v>
+      </c>
+      <c r="F54" t="s">
+        <v>10</v>
+      </c>
+      <c r="G54">
+        <v>0.77790000000000004</v>
+      </c>
+      <c r="H54">
+        <v>41.72</v>
+      </c>
+      <c r="I54" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>79</v>
+      </c>
+      <c r="B55" t="s">
+        <v>27</v>
+      </c>
+      <c r="C55" t="s">
+        <v>11</v>
+      </c>
+      <c r="D55">
+        <v>0.9546</v>
+      </c>
+      <c r="E55">
+        <v>31.97</v>
+      </c>
+      <c r="F55" t="s">
+        <v>11</v>
+      </c>
+      <c r="G55">
+        <v>0.93659999999999999</v>
+      </c>
+      <c r="H55">
+        <v>39.85</v>
+      </c>
+      <c r="I55" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
         <v>80</v>
       </c>
-      <c r="B51" t="s">
-        <v>36</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D51">
-        <v>0.38019999999999998</v>
-      </c>
-      <c r="E51">
-        <v>92.5</v>
-      </c>
-      <c r="F51" s="1" t="s">
+      <c r="B56" t="s">
+        <v>26</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D56">
+        <v>0.48780000000000001</v>
+      </c>
+      <c r="E56">
+        <v>32.86</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G56">
+        <v>0.37219999999999998</v>
+      </c>
+      <c r="H56">
+        <v>41.48</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>81</v>
+      </c>
+      <c r="B57" t="s">
+        <v>32</v>
+      </c>
+      <c r="C57" t="s">
+        <v>19</v>
+      </c>
+      <c r="D57">
+        <v>0.60229999999999995</v>
+      </c>
+      <c r="E57">
+        <v>30.18</v>
+      </c>
+      <c r="F57" t="s">
+        <v>19</v>
+      </c>
+      <c r="G57">
+        <v>0.57809999999999995</v>
+      </c>
+      <c r="H57">
+        <v>40.67</v>
+      </c>
+      <c r="I57" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>82</v>
+      </c>
+      <c r="B58" t="s">
+        <v>26</v>
+      </c>
+      <c r="C58" t="s">
+        <v>19</v>
+      </c>
+      <c r="D58">
+        <v>0.41349999999999998</v>
+      </c>
+      <c r="E58">
+        <v>30.98</v>
+      </c>
+      <c r="F58" t="s">
+        <v>19</v>
+      </c>
+      <c r="G58">
+        <v>0.41120000000000001</v>
+      </c>
+      <c r="H58">
+        <v>40.76</v>
+      </c>
+      <c r="I58" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>83</v>
+      </c>
+      <c r="B59" t="s">
+        <v>11</v>
+      </c>
+      <c r="C59" t="s">
+        <v>11</v>
+      </c>
+      <c r="D59">
+        <v>0.75190000000000001</v>
+      </c>
+      <c r="E59">
+        <v>29.03</v>
+      </c>
+      <c r="F59" t="s">
+        <v>11</v>
+      </c>
+      <c r="G59">
+        <v>0.9153</v>
+      </c>
+      <c r="H59">
+        <v>41.06</v>
+      </c>
+      <c r="I59" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>84</v>
+      </c>
+      <c r="B60" t="s">
+        <v>34</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D60">
+        <v>0.254</v>
+      </c>
+      <c r="E60">
+        <v>28.68</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G60">
+        <v>0.51749999999999996</v>
+      </c>
+      <c r="H60">
+        <v>43.75</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>85</v>
+      </c>
+      <c r="B61" t="s">
+        <v>11</v>
+      </c>
+      <c r="C61" t="s">
+        <v>29</v>
+      </c>
+      <c r="D61">
+        <v>0.51749999999999996</v>
+      </c>
+      <c r="E61">
+        <v>26.51</v>
+      </c>
+      <c r="F61" t="s">
+        <v>29</v>
+      </c>
+      <c r="G61">
+        <v>0.78680000000000005</v>
+      </c>
+      <c r="H61">
+        <v>39.340000000000003</v>
+      </c>
+      <c r="I61" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>86</v>
+      </c>
+      <c r="B62" t="s">
+        <v>27</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G51">
-        <v>0.22800000000000001</v>
-      </c>
-      <c r="H51">
-        <v>124.3</v>
-      </c>
-      <c r="I51" s="1" t="s">
-        <v>16</v>
+      <c r="D62">
+        <v>0.58340000000000003</v>
+      </c>
+      <c r="E62">
+        <v>27.99</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G62">
+        <v>0.17249999999999999</v>
+      </c>
+      <c r="H62">
+        <v>38.99</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>87</v>
+      </c>
+      <c r="B63" t="s">
+        <v>11</v>
+      </c>
+      <c r="C63" t="s">
+        <v>32</v>
+      </c>
+      <c r="D63">
+        <v>0.9698</v>
+      </c>
+      <c r="E63">
+        <v>28.55</v>
+      </c>
+      <c r="F63" t="s">
+        <v>32</v>
+      </c>
+      <c r="G63">
+        <v>0.99709999999999999</v>
+      </c>
+      <c r="H63">
+        <v>34.26</v>
+      </c>
+      <c r="I63" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>88</v>
+      </c>
+      <c r="B64" t="s">
+        <v>27</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D64">
+        <v>0.24990000000000001</v>
+      </c>
+      <c r="E64">
+        <v>29.46</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G64">
+        <v>0.48</v>
+      </c>
+      <c r="H64">
+        <v>38.4</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>89</v>
+      </c>
+      <c r="B65" t="s">
+        <v>90</v>
+      </c>
+      <c r="C65" t="s">
+        <v>90</v>
+      </c>
+      <c r="D65">
+        <v>0.30680000000000002</v>
+      </c>
+      <c r="E65">
+        <v>25.26</v>
+      </c>
+      <c r="F65" t="s">
+        <v>90</v>
+      </c>
+      <c r="G65">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="H65">
+        <v>36.04</v>
+      </c>
+      <c r="I65" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>91</v>
+      </c>
+      <c r="B66" t="s">
+        <v>26</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D66">
+        <v>0.64690000000000003</v>
+      </c>
+      <c r="E66">
+        <v>25.73</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G66">
+        <v>0.38540000000000002</v>
+      </c>
+      <c r="H66">
+        <v>41.97</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>92</v>
+      </c>
+      <c r="B67" t="s">
+        <v>32</v>
+      </c>
+      <c r="C67" t="s">
+        <v>10</v>
+      </c>
+      <c r="D67">
+        <v>0.47410000000000002</v>
+      </c>
+      <c r="E67">
+        <v>26.57</v>
+      </c>
+      <c r="F67" t="s">
+        <v>10</v>
+      </c>
+      <c r="G67">
+        <v>0.3009</v>
+      </c>
+      <c r="H67">
+        <v>36.869999999999997</v>
+      </c>
+      <c r="I67" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>93</v>
+      </c>
+      <c r="B68" t="s">
+        <v>94</v>
+      </c>
+      <c r="C68" t="s">
+        <v>11</v>
+      </c>
+      <c r="D68">
+        <v>0.94769999999999999</v>
+      </c>
+      <c r="E68">
+        <v>27.94</v>
+      </c>
+      <c r="F68" t="s">
+        <v>11</v>
+      </c>
+      <c r="G68">
+        <v>0.90180000000000005</v>
+      </c>
+      <c r="H68">
+        <v>42.74</v>
+      </c>
+      <c r="I68" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>95</v>
+      </c>
+      <c r="B69" t="s">
+        <v>27</v>
+      </c>
+      <c r="C69" t="s">
+        <v>11</v>
+      </c>
+      <c r="D69">
+        <v>0.7782</v>
+      </c>
+      <c r="E69">
+        <v>29.24</v>
+      </c>
+      <c r="F69" t="s">
+        <v>11</v>
+      </c>
+      <c r="G69">
+        <v>0.75039999999999996</v>
+      </c>
+      <c r="H69">
+        <v>35.69</v>
+      </c>
+      <c r="I69" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>96</v>
+      </c>
+      <c r="B70" t="s">
+        <v>32</v>
+      </c>
+      <c r="C70" t="s">
+        <v>10</v>
+      </c>
+      <c r="D70">
+        <v>0.47589999999999999</v>
+      </c>
+      <c r="E70">
+        <v>30.99</v>
+      </c>
+      <c r="F70" t="s">
+        <v>10</v>
+      </c>
+      <c r="G70">
+        <v>0.49259999999999998</v>
+      </c>
+      <c r="H70">
+        <v>41.27</v>
+      </c>
+      <c r="I70" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>97</v>
+      </c>
+      <c r="B71" t="s">
+        <v>26</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D71">
+        <v>0.31319999999999998</v>
+      </c>
+      <c r="E71">
+        <v>26.44</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G71">
+        <v>0.16869999999999999</v>
+      </c>
+      <c r="H71">
+        <v>40.86</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>98</v>
+      </c>
+      <c r="B72" t="s">
+        <v>90</v>
+      </c>
+      <c r="C72" t="s">
+        <v>32</v>
+      </c>
+      <c r="D72">
+        <v>0.93020000000000003</v>
+      </c>
+      <c r="E72">
+        <v>27.57</v>
+      </c>
+      <c r="F72" t="s">
+        <v>32</v>
+      </c>
+      <c r="G72">
+        <v>0.98560000000000003</v>
+      </c>
+      <c r="H72">
+        <v>38.520000000000003</v>
+      </c>
+      <c r="I72" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>99</v>
+      </c>
+      <c r="B73" t="s">
+        <v>11</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D73">
+        <v>0.26350000000000001</v>
+      </c>
+      <c r="E73">
+        <v>30.64</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G73">
+        <v>0.37569999999999998</v>
+      </c>
+      <c r="H73">
+        <v>42.92</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>100</v>
+      </c>
+      <c r="B74" t="s">
+        <v>11</v>
+      </c>
+      <c r="C74" t="s">
+        <v>10</v>
+      </c>
+      <c r="D74">
+        <v>0.59060000000000001</v>
+      </c>
+      <c r="E74">
+        <v>26.93</v>
+      </c>
+      <c r="F74" t="s">
+        <v>10</v>
+      </c>
+      <c r="G74">
+        <v>0.55410000000000004</v>
+      </c>
+      <c r="H74">
+        <v>34.28</v>
+      </c>
+      <c r="I74" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>101</v>
+      </c>
+      <c r="B75" t="s">
+        <v>102</v>
+      </c>
+      <c r="C75" t="s">
+        <v>56</v>
+      </c>
+      <c r="D75">
+        <v>0.47570000000000001</v>
+      </c>
+      <c r="E75">
+        <v>27.45</v>
+      </c>
+      <c r="F75" t="s">
+        <v>56</v>
+      </c>
+      <c r="G75">
+        <v>0.53590000000000004</v>
+      </c>
+      <c r="H75">
+        <v>40.33</v>
+      </c>
+      <c r="I75" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>103</v>
+      </c>
+      <c r="B76" t="s">
+        <v>32</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D76">
+        <v>0.37519999999999998</v>
+      </c>
+      <c r="E76">
+        <v>24.16</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G76">
+        <v>0.27439999999999998</v>
+      </c>
+      <c r="H76">
+        <v>35.44</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>104</v>
+      </c>
+      <c r="B77" t="s">
+        <v>27</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D77">
+        <v>0.29870000000000002</v>
+      </c>
+      <c r="E77">
+        <v>23.66</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G77">
+        <v>0.2417</v>
+      </c>
+      <c r="H77">
+        <v>49</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>105</v>
+      </c>
+      <c r="B78" t="s">
+        <v>34</v>
+      </c>
+      <c r="C78" t="s">
+        <v>29</v>
+      </c>
+      <c r="D78">
+        <v>0.79400000000000004</v>
+      </c>
+      <c r="E78">
+        <v>28.62</v>
+      </c>
+      <c r="F78" t="s">
+        <v>29</v>
+      </c>
+      <c r="G78">
+        <v>0.87129999999999996</v>
+      </c>
+      <c r="H78">
+        <v>40.32</v>
+      </c>
+      <c r="I78" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>106</v>
+      </c>
+      <c r="B79" t="s">
+        <v>27</v>
+      </c>
+      <c r="C79" t="s">
+        <v>49</v>
+      </c>
+      <c r="D79">
+        <v>0.77170000000000005</v>
+      </c>
+      <c r="E79">
+        <v>24.03</v>
+      </c>
+      <c r="F79" t="s">
+        <v>49</v>
+      </c>
+      <c r="G79">
+        <v>0.78979999999999995</v>
+      </c>
+      <c r="H79">
+        <v>38.15</v>
+      </c>
+      <c r="I79" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>107</v>
+      </c>
+      <c r="B80" t="s">
+        <v>90</v>
+      </c>
+      <c r="C80" t="s">
+        <v>32</v>
+      </c>
+      <c r="D80">
+        <v>0.98609999999999998</v>
+      </c>
+      <c r="E80">
+        <v>26.77</v>
+      </c>
+      <c r="F80" t="s">
+        <v>32</v>
+      </c>
+      <c r="G80">
+        <v>0.99450000000000005</v>
+      </c>
+      <c r="H80">
+        <v>36.840000000000003</v>
+      </c>
+      <c r="I80" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>108</v>
+      </c>
+      <c r="B81" t="s">
+        <v>94</v>
+      </c>
+      <c r="C81" t="s">
+        <v>56</v>
+      </c>
+      <c r="D81">
+        <v>0.54749999999999999</v>
+      </c>
+      <c r="E81">
+        <v>22.81</v>
+      </c>
+      <c r="F81" t="s">
+        <v>56</v>
+      </c>
+      <c r="G81">
+        <v>0.40339999999999998</v>
+      </c>
+      <c r="H81">
+        <v>37.31</v>
+      </c>
+      <c r="I81" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>109</v>
+      </c>
+      <c r="B82" t="s">
+        <v>90</v>
+      </c>
+      <c r="C82" t="s">
+        <v>10</v>
+      </c>
+      <c r="D82">
+        <v>0.52380000000000004</v>
+      </c>
+      <c r="E82">
+        <v>39.93</v>
+      </c>
+      <c r="F82" t="s">
+        <v>10</v>
+      </c>
+      <c r="G82">
+        <v>0.61750000000000005</v>
+      </c>
+      <c r="H82">
+        <v>40.78</v>
+      </c>
+      <c r="I82" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>110</v>
+      </c>
+      <c r="B83" t="s">
+        <v>102</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D83">
+        <v>0.73040000000000005</v>
+      </c>
+      <c r="E83">
+        <v>27.69</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G83">
+        <v>0.20180000000000001</v>
+      </c>
+      <c r="H83">
+        <v>39.36</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>111</v>
+      </c>
+      <c r="B84" t="s">
+        <v>90</v>
+      </c>
+      <c r="C84" t="s">
+        <v>10</v>
+      </c>
+      <c r="D84">
+        <v>0.5948</v>
+      </c>
+      <c r="E84">
+        <v>25.51</v>
+      </c>
+      <c r="F84" t="s">
+        <v>10</v>
+      </c>
+      <c r="G84">
+        <v>0.43709999999999999</v>
+      </c>
+      <c r="H84">
+        <v>51.88</v>
+      </c>
+      <c r="I84" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>112</v>
+      </c>
+      <c r="B85" t="s">
+        <v>32</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D85">
+        <v>0.60050000000000003</v>
+      </c>
+      <c r="E85">
+        <v>24.38</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G85">
+        <v>0.42830000000000001</v>
+      </c>
+      <c r="H85">
+        <v>40.65</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>113</v>
+      </c>
+      <c r="B86" t="s">
+        <v>27</v>
+      </c>
+      <c r="C86" t="s">
+        <v>32</v>
+      </c>
+      <c r="D86">
+        <v>0.96089999999999998</v>
+      </c>
+      <c r="E86">
+        <v>28.26</v>
+      </c>
+      <c r="F86" t="s">
+        <v>32</v>
+      </c>
+      <c r="G86">
+        <v>0.99750000000000005</v>
+      </c>
+      <c r="H86">
+        <v>38.18</v>
+      </c>
+      <c r="I86" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>114</v>
+      </c>
+      <c r="B87" t="s">
+        <v>27</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D87">
+        <v>0.58340000000000003</v>
+      </c>
+      <c r="E87">
+        <v>29.27</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G87">
+        <v>0.78169999999999995</v>
+      </c>
+      <c r="H87">
+        <v>37.49</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>115</v>
+      </c>
+      <c r="B88" t="s">
+        <v>11</v>
+      </c>
+      <c r="C88" t="s">
+        <v>10</v>
+      </c>
+      <c r="D88">
+        <v>0.64790000000000003</v>
+      </c>
+      <c r="E88">
+        <v>28.91</v>
+      </c>
+      <c r="F88" t="s">
+        <v>10</v>
+      </c>
+      <c r="G88">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="H88">
+        <v>48.15</v>
+      </c>
+      <c r="I88" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>116</v>
+      </c>
+      <c r="B89" t="s">
+        <v>102</v>
+      </c>
+      <c r="C89" t="s">
+        <v>37</v>
+      </c>
+      <c r="D89">
+        <v>0.48320000000000002</v>
+      </c>
+      <c r="E89">
+        <v>35.549999999999997</v>
+      </c>
+      <c r="F89" t="s">
+        <v>37</v>
+      </c>
+      <c r="G89">
+        <v>0.35920000000000002</v>
+      </c>
+      <c r="H89">
+        <v>49</v>
+      </c>
+      <c r="I89" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>117</v>
+      </c>
+      <c r="B90" t="s">
+        <v>32</v>
+      </c>
+      <c r="C90" t="s">
+        <v>19</v>
+      </c>
+      <c r="D90">
+        <v>0.66800000000000004</v>
+      </c>
+      <c r="E90">
+        <v>35.04</v>
+      </c>
+      <c r="F90" t="s">
+        <v>19</v>
+      </c>
+      <c r="G90">
+        <v>0.4083</v>
+      </c>
+      <c r="H90">
+        <v>38.92</v>
+      </c>
+      <c r="I90" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>118</v>
+      </c>
+      <c r="B91" t="s">
+        <v>27</v>
+      </c>
+      <c r="C91" t="s">
+        <v>49</v>
+      </c>
+      <c r="D91">
+        <v>0.67930000000000001</v>
+      </c>
+      <c r="E91">
+        <v>26.84</v>
+      </c>
+      <c r="F91" t="s">
+        <v>49</v>
+      </c>
+      <c r="G91">
+        <v>0.53369999999999995</v>
+      </c>
+      <c r="H91">
+        <v>34.020000000000003</v>
+      </c>
+      <c r="I91" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>119</v>
+      </c>
+      <c r="B92" t="s">
+        <v>32</v>
+      </c>
+      <c r="C92" t="s">
+        <v>32</v>
+      </c>
+      <c r="D92">
+        <v>0.98519999999999996</v>
+      </c>
+      <c r="E92">
+        <v>30.51</v>
+      </c>
+      <c r="F92" t="s">
+        <v>32</v>
+      </c>
+      <c r="G92">
+        <v>0.99309999999999998</v>
+      </c>
+      <c r="H92">
+        <v>41.95</v>
+      </c>
+      <c r="I92" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>120</v>
+      </c>
+      <c r="B93" t="s">
+        <v>34</v>
+      </c>
+      <c r="C93" t="s">
+        <v>56</v>
+      </c>
+      <c r="D93">
+        <v>0.82669999999999999</v>
+      </c>
+      <c r="E93">
+        <v>33.71</v>
+      </c>
+      <c r="F93" t="s">
+        <v>56</v>
+      </c>
+      <c r="G93">
+        <v>0.68930000000000002</v>
+      </c>
+      <c r="H93">
+        <v>36.43</v>
+      </c>
+      <c r="I93" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>121</v>
+      </c>
+      <c r="B94" t="s">
+        <v>11</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D94">
+        <v>0.40310000000000001</v>
+      </c>
+      <c r="E94">
+        <v>26.31</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G94">
+        <v>0.35089999999999999</v>
+      </c>
+      <c r="H94">
+        <v>38.11</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>122</v>
+      </c>
+      <c r="B95" t="s">
+        <v>102</v>
+      </c>
+      <c r="C95" t="s">
+        <v>18</v>
+      </c>
+      <c r="D95">
+        <v>0.38900000000000001</v>
+      </c>
+      <c r="E95">
+        <v>29.18</v>
+      </c>
+      <c r="F95" t="s">
+        <v>18</v>
+      </c>
+      <c r="G95">
+        <v>0.2611</v>
+      </c>
+      <c r="H95">
+        <v>41.46</v>
+      </c>
+      <c r="I95" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>123</v>
+      </c>
+      <c r="B96" t="s">
+        <v>32</v>
+      </c>
+      <c r="C96" t="s">
+        <v>29</v>
+      </c>
+      <c r="D96">
+        <v>0.7782</v>
+      </c>
+      <c r="E96">
+        <v>28.57</v>
+      </c>
+      <c r="F96" t="s">
+        <v>29</v>
+      </c>
+      <c r="G96">
+        <v>0.81459999999999999</v>
+      </c>
+      <c r="H96">
+        <v>45.2</v>
+      </c>
+      <c r="I96" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>124</v>
+      </c>
+      <c r="B97" t="s">
+        <v>27</v>
+      </c>
+      <c r="C97" t="s">
+        <v>49</v>
+      </c>
+      <c r="D97">
+        <v>0.67290000000000005</v>
+      </c>
+      <c r="E97">
+        <v>31.33</v>
+      </c>
+      <c r="F97" t="s">
+        <v>49</v>
+      </c>
+      <c r="G97">
+        <v>0.64800000000000002</v>
+      </c>
+      <c r="H97">
+        <v>46.31</v>
+      </c>
+      <c r="I97" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>125</v>
+      </c>
+      <c r="B98" t="s">
+        <v>34</v>
+      </c>
+      <c r="C98" t="s">
+        <v>10</v>
+      </c>
+      <c r="D98">
+        <v>0.39979999999999999</v>
+      </c>
+      <c r="E98">
+        <v>29.78</v>
+      </c>
+      <c r="F98" t="s">
+        <v>10</v>
+      </c>
+      <c r="G98">
+        <v>0.44429999999999997</v>
+      </c>
+      <c r="H98">
+        <v>42.13</v>
+      </c>
+      <c r="I98" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>126</v>
+      </c>
+      <c r="B99" t="s">
+        <v>27</v>
+      </c>
+      <c r="C99" t="s">
+        <v>56</v>
+      </c>
+      <c r="D99">
+        <v>0.7903</v>
+      </c>
+      <c r="E99">
+        <v>26</v>
+      </c>
+      <c r="F99" t="s">
+        <v>56</v>
+      </c>
+      <c r="G99">
+        <v>0.72309999999999997</v>
+      </c>
+      <c r="H99">
+        <v>44.51</v>
+      </c>
+      <c r="I99" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>127</v>
+      </c>
+      <c r="B100" t="s">
+        <v>11</v>
+      </c>
+      <c r="C100" t="s">
+        <v>32</v>
+      </c>
+      <c r="D100">
+        <v>0.99099999999999999</v>
+      </c>
+      <c r="E100">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F100" t="s">
+        <v>32</v>
+      </c>
+      <c r="G100">
+        <v>0.99890000000000001</v>
+      </c>
+      <c r="H100">
+        <v>42.07</v>
+      </c>
+      <c r="I100" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>128</v>
+      </c>
+      <c r="B101" t="s">
+        <v>102</v>
+      </c>
+      <c r="C101" t="s">
+        <v>15</v>
+      </c>
+      <c r="D101">
+        <v>0.6986</v>
+      </c>
+      <c r="E101">
+        <v>27.86</v>
+      </c>
+      <c r="F101" t="s">
+        <v>15</v>
+      </c>
+      <c r="G101">
+        <v>0.2631</v>
+      </c>
+      <c r="H101">
+        <v>39.75</v>
+      </c>
+      <c r="I101" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
